--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260812.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>837,897</t>
+          <t>142,921</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>142,921</t>
+          <t>837,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>3,607,981</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,607,981</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>404,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>404,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>804,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>804,000</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,039,121</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,822,000</t>
+          <t>1,039,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>119,000</t>
+          <t>1,822,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>184,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>184,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>74,000</t>
+          <t>348,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>348,000</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
